--- a/artfynd/A 38366-2021 artfynd.xlsx
+++ b/artfynd/A 38366-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38366-2021 artfynd.xlsx
+++ b/artfynd/A 38366-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119103613</v>
+        <v>119567022</v>
       </c>
       <c r="B3" t="n">
-        <v>106416</v>
+        <v>57272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,58 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>100020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Havregölet, skogsklocka, Srm</t>
+          <t>Havregölet syd, Havregölet, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580972</v>
+        <v>581017</v>
       </c>
       <c r="R3" t="n">
-        <v>6513862</v>
+        <v>6513588</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,24 +876,14 @@
           <t>Kila</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>D-Nyk-0197</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>vägkanter</t>
+          <t>2023-12-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,140 +892,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Jonatan Axelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>bert lindgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>119567022</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57272</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100020</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Berguv</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bubo bubo</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Havregölet syd, Havregölet, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>581017</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6513588</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Kila</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-12-16</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-12-16</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
           <t>Jonatan Axelsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Jonatan Axelsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38366-2021 artfynd.xlsx
+++ b/artfynd/A 38366-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>236823</v>
+        <v>230878</v>
       </c>
       <c r="B2" t="n">
-        <v>104642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580971.8271698249</v>
+        <v>580972</v>
       </c>
       <c r="R2" t="n">
-        <v>6513862.475812817</v>
+        <v>6513862</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1978-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1978-08-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör: Erik Genberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>D-län Floraväktarna, Hans-Erik Wanntorp</t>
+          <t>D-län Floraväktarna</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -799,12 +789,7 @@
         <v>119567022</v>
       </c>
       <c r="B3" t="n">
-        <v>57272</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
